--- a/public/test-data/pph21-filled.xlsx
+++ b/public/test-data/pph21-filled.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="PPh21 직원 데이터" sheetId="1" r:id="rId1"/>
-    <sheet name="안내 - Petunjuk" sheetId="2" r:id="rId2"/>
+    <sheet name="PPh21" sheetId="1" r:id="rId1"/>
+    <sheet name="Petunjuk (Guideline)" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -398,487 +398,565 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH6"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="20.83203125" customWidth="1"/>
-    <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="20.83203125" customWidth="1"/>
-    <col min="20" max="20" width="20.83203125" customWidth="1"/>
-    <col min="21" max="21" width="20.83203125" customWidth="1"/>
-    <col min="22" max="22" width="20.83203125" customWidth="1"/>
-    <col min="23" max="23" width="20.83203125" customWidth="1"/>
-    <col min="24" max="24" width="20.83203125" customWidth="1"/>
-    <col min="25" max="25" width="20.83203125" customWidth="1"/>
-    <col min="26" max="26" width="20.83203125" customWidth="1"/>
-    <col min="27" max="27" width="20.83203125" customWidth="1"/>
-    <col min="28" max="28" width="20.83203125" customWidth="1"/>
-    <col min="29" max="29" width="20.83203125" customWidth="1"/>
-    <col min="30" max="30" width="20.83203125" customWidth="1"/>
-    <col min="31" max="31" width="20.83203125" customWidth="1"/>
-    <col min="32" max="32" width="20.83203125" customWidth="1"/>
-    <col min="33" max="33" width="20.83203125" customWidth="1"/>
-    <col min="34" max="34" width="20.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:AQ6"/>
   <sheetData>
-    <row r="1">
+    <row r="1" xml:space="preserve">
       <c r="A1" t="str">
+        <v>employee_number</v>
+      </c>
+      <c r="B1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Employment status_x000d_
+(Pegawai Tetap: 1, Pegawai Tidak Tetap: 2, Bukan Pegawai: 3)</v>
+      </c>
+      <c r="C1" t="str">
         <v>employee_name</v>
       </c>
-      <c r="B1" t="str">
+      <c r="D1" t="str">
         <v>employee_npwp</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>employee_nik</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>ptkp_category</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str" xml:space="preserve">
+        <v xml:space="preserve">tax method_x000d_
+_gross/gross up</v>
+      </c>
+      <c r="H1" t="str">
         <v>gross_salary</v>
       </c>
-      <c r="F1" t="str">
+      <c r="I1" t="str">
         <v>position_allowance</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>overtime_pay</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>meal_allowance</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>transport_allowance</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>other_allowances</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
+        <v>natura_fasilitas bkn uang</v>
+      </c>
+      <c r="O1" t="str">
         <v>bonus</v>
       </c>
-      <c r="L1" t="str">
-        <v>thr</v>
-      </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
+        <v>THR</v>
+      </c>
+      <c r="Q1" t="str" xml:space="preserve">
+        <v xml:space="preserve">pinjaman gaji_x000d_
+_loan from salary</v>
+      </c>
+      <c r="R1" t="str" xml:space="preserve">
+        <v xml:space="preserve">potong gaji_x000d_
+_deduction from salary</v>
+      </c>
+      <c r="S1" t="str">
+        <v>jkk</v>
+      </c>
+      <c r="T1" t="str">
+        <v>jkm</v>
+      </c>
+      <c r="U1" t="str">
+        <v>jht_company</v>
+      </c>
+      <c r="V1" t="str">
+        <v>jp_company</v>
+      </c>
+      <c r="W1" t="str" xml:space="preserve">
+        <v xml:space="preserve">bpjs kesehatan_x000d_
+_company</v>
+      </c>
+      <c r="X1" t="str">
+        <v>JKP_company</v>
+      </c>
+      <c r="Y1" t="str">
         <v>jht_employee</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Z1" t="str">
         <v>jp_employee</v>
       </c>
-      <c r="O1" t="str">
-        <v>bpjs_kesehatan</v>
-      </c>
-      <c r="P1" t="str">
-        <v>other_deductions</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>worker_type</v>
-      </c>
-      <c r="R1" t="str">
-        <v>employee_number</v>
-      </c>
-      <c r="S1" t="str">
+      <c r="AA1" t="str" xml:space="preserve">
+        <v xml:space="preserve">bpjs kesehatan_x000d_
+_employee</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>JKP_employee</v>
+      </c>
+      <c r="AC1" t="str">
         <v>position</v>
       </c>
-      <c r="T1" t="str">
+      <c r="AD1" t="str">
         <v>department</v>
       </c>
-      <c r="U1" t="str">
-        <v>hire_date</v>
-      </c>
-      <c r="V1" t="str">
+      <c r="AE1" t="str">
+        <v>join_date</v>
+      </c>
+      <c r="AF1" t="str">
         <v>resign_date</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AG1" t="str">
         <v>birth_date</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AH1" t="str">
         <v>gender</v>
       </c>
-      <c r="Y1" t="str">
-        <v>marital_status</v>
-      </c>
-      <c r="Z1" t="str">
+      <c r="AI1" t="str">
         <v>email</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AJ1" t="str">
         <v>phone</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AK1" t="str">
         <v>address</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AL1" t="str">
         <v>bank_name</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AM1" t="str">
         <v>bank_account_no</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AN1" t="str">
         <v>bank_account_name</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AO1" t="str">
         <v>emergency_contact_name</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AP1" t="str">
         <v>emergency_contact_phone</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AQ1" t="str">
         <v>notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>EMP-001</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
         <v>Andi Wijaya</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
         <v>01.234.567.8-001.000</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>3201111111110001</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
         <v>K/2</v>
       </c>
-      <c r="E2">
+      <c r="G2" t="str">
+        <v>Gross</v>
+      </c>
+      <c r="H2">
         <v>15000000</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>2500000</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>300000</v>
       </c>
-      <c r="I2">
+      <c r="L2">
         <v>200000</v>
       </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
       <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2">
+        <v>100000</v>
+      </c>
+      <c r="T2">
+        <v>30000</v>
+      </c>
+      <c r="U2">
+        <v>450000</v>
+      </c>
+      <c r="V2">
         <v>300000</v>
       </c>
-      <c r="N2">
+      <c r="W2">
+        <v>600000</v>
+      </c>
+      <c r="X2">
+        <v>30000</v>
+      </c>
+      <c r="Y2">
+        <v>300000</v>
+      </c>
+      <c r="Z2">
         <v>150000</v>
       </c>
-      <c r="O2">
+      <c r="AA2">
         <v>150000</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>REGULAR</v>
-      </c>
-      <c r="R2" t="str">
-        <v>EMP-001</v>
-      </c>
-      <c r="S2" t="str">
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="str">
         <v>Senior Engineer</v>
       </c>
-      <c r="T2" t="str">
+      <c r="AD2" t="str">
         <v>IT</v>
       </c>
-      <c r="U2" t="str">
+      <c r="AE2" t="str">
         <v>2022-03-01</v>
       </c>
-      <c r="V2" t="str">
-        <v/>
-      </c>
-      <c r="W2" t="str">
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
         <v>1989-04-12</v>
       </c>
-      <c r="X2" t="str">
+      <c r="AH2" t="str">
         <v>M</v>
       </c>
-      <c r="Y2" t="str">
-        <v>MARRIED</v>
-      </c>
-      <c r="Z2" t="str">
+      <c r="AI2" t="str">
         <v>andi@example.com</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AJ2" t="str">
         <v>+62 811 1111 1111</v>
       </c>
-      <c r="AB2" t="str">
+      <c r="AK2" t="str">
         <v>Jl. Sudirman 10</v>
       </c>
-      <c r="AC2" t="str">
+      <c r="AL2" t="str">
         <v>BCA</v>
       </c>
-      <c r="AD2" t="str">
+      <c r="AM2" t="str">
         <v>1111111111</v>
       </c>
-      <c r="AE2" t="str">
+      <c r="AN2" t="str">
         <v>Andi Wijaya</v>
       </c>
-      <c r="AF2" t="str">
+      <c r="AO2" t="str">
         <v>Wati</v>
       </c>
-      <c r="AG2" t="str">
+      <c r="AP2" t="str">
         <v>+62 811 1111 1112</v>
       </c>
-      <c r="AH2" t="str">
+      <c r="AQ2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>EMP-002</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="str">
         <v>Sari Lestari</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
         <v>3202222222220002</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3" t="str">
         <v>TK/0</v>
       </c>
-      <c r="E3">
+      <c r="G3" t="str">
+        <v>Gross</v>
+      </c>
+      <c r="H3">
         <v>8000000</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>500000</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>300000</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>200000</v>
       </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3">
+        <v>60000</v>
+      </c>
+      <c r="T3">
+        <v>18000</v>
+      </c>
+      <c r="U3">
+        <v>240000</v>
+      </c>
+      <c r="V3">
         <v>160000</v>
       </c>
-      <c r="N3">
+      <c r="W3">
+        <v>320000</v>
+      </c>
+      <c r="X3">
+        <v>16000</v>
+      </c>
+      <c r="Y3">
+        <v>160000</v>
+      </c>
+      <c r="Z3">
         <v>80000</v>
       </c>
-      <c r="O3">
+      <c r="AA3">
         <v>80000</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>REGULAR</v>
-      </c>
-      <c r="R3" t="str">
-        <v>EMP-002</v>
-      </c>
-      <c r="S3" t="str">
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="str">
         <v>Analyst</v>
       </c>
-      <c r="T3" t="str">
+      <c r="AD3" t="str">
         <v>HR</v>
       </c>
-      <c r="U3" t="str">
+      <c r="AE3" t="str">
         <v>2024-08-15</v>
       </c>
-      <c r="V3" t="str">
-        <v/>
-      </c>
-      <c r="W3" t="str">
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
         <v>1996-09-25</v>
       </c>
-      <c r="X3" t="str">
+      <c r="AH3" t="str">
         <v>F</v>
       </c>
-      <c r="Y3" t="str">
-        <v>SINGLE</v>
-      </c>
-      <c r="Z3" t="str">
+      <c r="AI3" t="str">
         <v>sari@example.com</v>
       </c>
-      <c r="AA3" t="str">
+      <c r="AJ3" t="str">
         <v>+62 812 2222 2222</v>
       </c>
-      <c r="AB3" t="str">
+      <c r="AK3" t="str">
         <v>Jl. Thamrin 5</v>
       </c>
-      <c r="AC3" t="str">
+      <c r="AL3" t="str">
         <v>BCA</v>
       </c>
-      <c r="AD3" t="str">
+      <c r="AM3" t="str">
         <v>2222222222</v>
       </c>
-      <c r="AE3" t="str">
+      <c r="AN3" t="str">
         <v>Sari Lestari</v>
       </c>
-      <c r="AF3" t="str">
+      <c r="AO3" t="str">
         <v>Rini</v>
       </c>
-      <c r="AG3" t="str">
+      <c r="AP3" t="str">
         <v>+62 812 2222 2223</v>
       </c>
-      <c r="AH3" t="str">
+      <c r="AQ3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>EMP-003</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
         <v>Budi Hartono</v>
       </c>
-      <c r="B4" t="str">
+      <c r="D4" t="str">
         <v>02.345.678.9-002.000</v>
       </c>
-      <c r="C4" t="str">
+      <c r="E4" t="str">
         <v>3203333333330003</v>
       </c>
-      <c r="D4" t="str">
+      <c r="F4" t="str">
         <v>K/1</v>
       </c>
-      <c r="E4">
+      <c r="G4" t="str">
+        <v>Gross Up</v>
+      </c>
+      <c r="H4">
         <v>25000000</v>
       </c>
-      <c r="F4">
+      <c r="I4">
         <v>4000000</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>300000</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>200000</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4">
         <v>2083333</v>
       </c>
-      <c r="M4">
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4">
+        <v>150000</v>
+      </c>
+      <c r="T4">
+        <v>50000</v>
+      </c>
+      <c r="U4">
+        <v>750000</v>
+      </c>
+      <c r="V4">
         <v>500000</v>
       </c>
-      <c r="N4">
+      <c r="W4">
+        <v>1000000</v>
+      </c>
+      <c r="X4">
+        <v>50000</v>
+      </c>
+      <c r="Y4">
+        <v>500000</v>
+      </c>
+      <c r="Z4">
         <v>250000</v>
       </c>
-      <c r="O4">
+      <c r="AA4">
         <v>250000</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>REGULAR</v>
-      </c>
-      <c r="R4" t="str">
-        <v>EMP-003</v>
-      </c>
-      <c r="S4" t="str">
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="str">
         <v>Director</v>
       </c>
-      <c r="T4" t="str">
+      <c r="AD4" t="str">
         <v>Operations</v>
       </c>
-      <c r="U4" t="str">
+      <c r="AE4" t="str">
         <v>2020-01-15</v>
       </c>
-      <c r="V4" t="str">
-        <v/>
-      </c>
-      <c r="W4" t="str">
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
         <v>1982-11-08</v>
       </c>
-      <c r="X4" t="str">
+      <c r="AH4" t="str">
         <v>M</v>
       </c>
-      <c r="Y4" t="str">
-        <v>MARRIED</v>
-      </c>
-      <c r="Z4" t="str">
+      <c r="AI4" t="str">
         <v>budi@example.com</v>
       </c>
-      <c r="AA4" t="str">
+      <c r="AJ4" t="str">
         <v>+62 813 3333 3333</v>
       </c>
-      <c r="AB4" t="str">
+      <c r="AK4" t="str">
         <v>Jl. Gatot 88</v>
       </c>
-      <c r="AC4" t="str">
+      <c r="AL4" t="str">
         <v>Mandiri</v>
       </c>
-      <c r="AD4" t="str">
+      <c r="AM4" t="str">
         <v>3333333333</v>
       </c>
-      <c r="AE4" t="str">
+      <c r="AN4" t="str">
         <v>Budi Hartono</v>
       </c>
-      <c r="AF4" t="str">
+      <c r="AO4" t="str">
         <v>Sri</v>
       </c>
-      <c r="AG4" t="str">
+      <c r="AP4" t="str">
         <v>+62 813 3333 3334</v>
       </c>
-      <c r="AH4" t="str">
+      <c r="AQ4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>EMP-004</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="str">
         <v>Citra Wulandari</v>
       </c>
-      <c r="B5" t="str">
+      <c r="D5" t="str">
         <v>03.456.789.0-003.000</v>
       </c>
-      <c r="C5" t="str">
+      <c r="E5" t="str">
         <v>3204444444440004</v>
       </c>
-      <c r="D5" t="str">
+      <c r="F5" t="str">
         <v>TK/1</v>
       </c>
-      <c r="E5">
-        <v>12000000</v>
-      </c>
-      <c r="F5">
-        <v>1500000</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
+      <c r="G5" t="str">
+        <v>Gross</v>
       </c>
       <c r="H5">
-        <v>300000</v>
+        <v>6000000</v>
       </c>
       <c r="I5">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -890,99 +968,126 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>240000</v>
-      </c>
-      <c r="N5">
-        <v>120000</v>
+        <v>0</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
       </c>
       <c r="O5">
-        <v>120000</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5" t="str">
-        <v>REGULAR</v>
+        <v/>
       </c>
       <c r="R5" t="str">
-        <v>EMP-004</v>
+        <v/>
       </c>
       <c r="S5" t="str">
-        <v>Marketing Manager</v>
+        <v/>
       </c>
       <c r="T5" t="str">
-        <v>Marketing</v>
+        <v/>
       </c>
       <c r="U5" t="str">
-        <v>2023-05-20</v>
+        <v/>
       </c>
       <c r="V5" t="str">
         <v/>
       </c>
       <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v>Field Worker</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>Operations</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>2026-04-10</v>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
         <v>1992-06-30</v>
       </c>
-      <c r="X5" t="str">
+      <c r="AH5" t="str">
         <v>F</v>
       </c>
-      <c r="Y5" t="str">
-        <v>SINGLE</v>
-      </c>
-      <c r="Z5" t="str">
+      <c r="AI5" t="str">
         <v>citra@example.com</v>
       </c>
-      <c r="AA5" t="str">
+      <c r="AJ5" t="str">
         <v>+62 814 4444 4444</v>
       </c>
-      <c r="AB5" t="str">
+      <c r="AK5" t="str">
         <v>Jl. Cendana 22</v>
       </c>
-      <c r="AC5" t="str">
-        <v>BNI</v>
-      </c>
-      <c r="AD5" t="str">
-        <v>4444444444</v>
-      </c>
-      <c r="AE5" t="str">
+      <c r="AL5" t="str">
+        <v/>
+      </c>
+      <c r="AM5" t="str">
+        <v/>
+      </c>
+      <c r="AN5" t="str">
         <v>Citra Wulandari</v>
       </c>
-      <c r="AF5" t="str">
+      <c r="AO5" t="str">
         <v>Eka</v>
       </c>
-      <c r="AG5" t="str">
+      <c r="AP5" t="str">
         <v>+62 814 4444 4445</v>
       </c>
-      <c r="AH5" t="str">
-        <v/>
+      <c r="AQ5" t="str">
+        <v>6개월 단기 계약</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>EMP-005</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="str">
         <v>Dimas Pratama</v>
       </c>
-      <c r="B6" t="str">
+      <c r="D6" t="str">
         <v>04.567.890.1-004.000</v>
       </c>
-      <c r="C6" t="str">
+      <c r="E6" t="str">
         <v>3205555555550005</v>
       </c>
-      <c r="D6" t="str">
+      <c r="F6" t="str">
         <v>K/0</v>
       </c>
-      <c r="E6">
-        <v>18000000</v>
-      </c>
-      <c r="F6">
-        <v>2000000</v>
-      </c>
-      <c r="G6">
-        <v>500000</v>
+      <c r="G6" t="str">
+        <v>Gross</v>
       </c>
       <c r="H6">
-        <v>300000</v>
+        <v>3500000</v>
       </c>
       <c r="I6">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -994,134 +1099,994 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>360000</v>
-      </c>
-      <c r="N6">
-        <v>180000</v>
+        <v>0</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
       </c>
       <c r="O6">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6" t="str">
-        <v>REGULAR</v>
+        <v/>
       </c>
       <c r="R6" t="str">
-        <v>EMP-005</v>
+        <v/>
       </c>
       <c r="S6" t="str">
-        <v>Finance Manager</v>
+        <v/>
       </c>
       <c r="T6" t="str">
-        <v>Finance</v>
+        <v/>
       </c>
       <c r="U6" t="str">
-        <v>2021-09-01</v>
+        <v/>
       </c>
       <c r="V6" t="str">
         <v/>
       </c>
       <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <v/>
+      </c>
+      <c r="AC6" t="str">
+        <v>External Consultant</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>Project</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="AF6" t="str">
+        <v/>
+      </c>
+      <c r="AG6" t="str">
         <v>1985-12-03</v>
       </c>
-      <c r="X6" t="str">
+      <c r="AH6" t="str">
         <v>M</v>
       </c>
-      <c r="Y6" t="str">
-        <v>MARRIED</v>
-      </c>
-      <c r="Z6" t="str">
+      <c r="AI6" t="str">
         <v>dimas@example.com</v>
       </c>
-      <c r="AA6" t="str">
+      <c r="AJ6" t="str">
         <v>+62 815 5555 5555</v>
       </c>
-      <c r="AB6" t="str">
+      <c r="AK6" t="str">
         <v>Jl. Asia Afrika 33</v>
       </c>
-      <c r="AC6" t="str">
-        <v>Mandiri</v>
-      </c>
-      <c r="AD6" t="str">
-        <v>5555555555</v>
-      </c>
-      <c r="AE6" t="str">
+      <c r="AL6" t="str">
+        <v/>
+      </c>
+      <c r="AM6" t="str">
+        <v/>
+      </c>
+      <c r="AN6" t="str">
         <v>Dimas Pratama</v>
       </c>
-      <c r="AF6" t="str">
+      <c r="AO6" t="str">
         <v>Maya</v>
       </c>
-      <c r="AG6" t="str">
+      <c r="AP6" t="str">
         <v>+62 815 5555 5556</v>
       </c>
-      <c r="AH6" t="str">
-        <v/>
+      <c r="AQ6" t="str">
+        <v>프로젝트 단위 계약</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AQ6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:F44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>컬럼 / Column</v>
+        <v>Column</v>
       </c>
       <c r="B1" t="str">
-        <v>설명 / Keterangan</v>
+        <v>Indonesia</v>
+      </c>
+      <c r="C1" t="str">
+        <v>English</v>
+      </c>
+      <c r="D1" t="str">
+        <v>한국어</v>
+      </c>
+      <c r="E1" t="str">
+        <v>中文</v>
+      </c>
+      <c r="F1" t="str">
+        <v>日本語</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>employee_name</v>
+        <v>employee_number</v>
       </c>
       <c r="B2" t="str">
-        <v>직원 이름 (필수)</v>
+        <v>Nomor atau kode karyawan. Contoh: EMP-001.</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Employee ID or code. Example: EMP-001.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>직원 번호 또는 직원 코드입니다. 예: EMP-001.</v>
+      </c>
+      <c r="E2" t="str">
+        <v>员工编号或员工代码。例如：EMP-001。</v>
+      </c>
+      <c r="F2" t="str">
+        <v>従業員番号または従業員コードです。例：EMP-001。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ptkp_category</v>
+        <v>employment_status</v>
       </c>
       <c r="B3" t="str">
-        <v>TK/0, TK/1, K/0, K/1, K/2 ...</v>
+        <v>Status karyawan. Isi 1 = Pegawai Tetap, 2 = Pegawai Tidak Tetap, 3 = Bukan Pegawai.</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Employment status. Enter 1 = permanent employee, 2 = non-permanent employee, 3 = non-employee.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>고용 상태입니다. 1 = 정규직, 2 = 비정규/일용직, 3 = 비직원.</v>
+      </c>
+      <c r="E3" t="str">
+        <v>雇佣状态。填写 1 = 固定员工，2 = 非固定员工，3 = 非员工。</v>
+      </c>
+      <c r="F3" t="str">
+        <v>雇用区分です。1 = 正社員、2 = 非正規社員、3 = 従業員以外。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>gross_salary</v>
+        <v>employee_name</v>
       </c>
       <c r="B4" t="str">
-        <v>월 기본급 (필수, 숫자)</v>
+        <v>Nama lengkap karyawan.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Full name of the employee.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>직원의 전체 이름입니다.</v>
+      </c>
+      <c r="E4" t="str">
+        <v>员工全名。</v>
+      </c>
+      <c r="F4" t="str">
+        <v>従業員の氏名です。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>worker_type</v>
+        <v>employee_npwp</v>
       </c>
       <c r="B5" t="str">
-        <v>REGULAR / CONTRACT / DAILY / FREELANCER / COMMISSIONER</v>
+        <v>NPWP karyawan. Jika belum ada, kosongkan atau isi sesuai data yang tersedia.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Employee NPWP. Leave blank if not available.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>직원 NPWP입니다. 없는 경우 비워둘 수 있습니다.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>员工 NPWP。如无，可留空。</v>
+      </c>
+      <c r="F5" t="str">
+        <v>従業員のNPWPです。ない場合は空欄にします。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>hire_date</v>
+        <v>employee_nik</v>
       </c>
       <c r="B6" t="str">
-        <v>입사일 YYYY-MM-DD</v>
+        <v>Nomor NIK/KTP karyawan.</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Employee NIK/KTP number.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>직원 NIK/KTP 번호입니다.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>员工 NIK/KTP 号码。</v>
+      </c>
+      <c r="F6" t="str">
+        <v>従業員のNIK/KTP番号です。</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ptkp_category</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Status PTKP karyawan. Contoh: TK/0, TK/1, K/0, K/1, K/2, K/3.</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Employee PTKP category. Example: TK/0, TK/1, K/0, K/1, K/2, K/3.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>직원의 PTKP 세무상 가족상태입니다. 예: TK/0, K/1.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>员工 PTKP 类别。例如：TK/0, K/1。</v>
+      </c>
+      <c r="F7" t="str">
+        <v>従業員のPTKP区分です。例：TK/0、K/1。</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>tax_method</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Metode pajak. Isi Gross atau Gross Up.</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Tax method. Enter Gross or Gross Up.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>세금 계산 방식입니다. Gross 또는 Gross Up을 입력합니다.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>税务计算方式。填写 Gross 或 Gross Up。</v>
+      </c>
+      <c r="F8" t="str">
+        <v>税計算方式です。Gross または Gross Up を入力します。</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>gross_salary</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Gaji pokok bruto per bulan sebelum potongan.</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Monthly gross basic salary before deductions.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>공제 전 월 기본급입니다.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>扣除前的月基本工资。</v>
+      </c>
+      <c r="F9" t="str">
+        <v>控除前の月額基本給です。</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>position_allowance</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Tunjangan jabatan. Jika tidak ada, isi 0.</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Position allowance. Enter 0 if not applicable.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>직책수당입니다. 없으면 0을 입력합니다.</v>
+      </c>
+      <c r="E10" t="str">
+        <v>职务津贴。如无，填写 0。</v>
+      </c>
+      <c r="F10" t="str">
+        <v>役職手当です。ない場合は0を入力します。</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>overtime_pay</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Upah lembur bulan tersebut.</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Overtime pay for the month.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>해당 월의 초과근무수당입니다.</v>
+      </c>
+      <c r="E11" t="str">
+        <v>当月加班费。</v>
+      </c>
+      <c r="F11" t="str">
+        <v>当月の残業手当です。</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>meal_allowance</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Tunjangan makan.</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Meal allowance.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>식대 수당입니다.</v>
+      </c>
+      <c r="E12" t="str">
+        <v>餐费津贴。</v>
+      </c>
+      <c r="F12" t="str">
+        <v>食事手当です。</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>transport_allowance</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Tunjangan transportasi.</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Transportation allowance.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>교통비 수당입니다.</v>
+      </c>
+      <c r="E13" t="str">
+        <v>交通津贴。</v>
+      </c>
+      <c r="F13" t="str">
+        <v>交通手当です。</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>other_allowances</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Tunjangan lain-lain. Jika tidak ada, isi 0.</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Other allowances. Enter 0 if none.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>기타 수당입니다. 없으면 0을 입력합니다.</v>
+      </c>
+      <c r="E14" t="str">
+        <v>其他津贴。如无，填写 0。</v>
+      </c>
+      <c r="F14" t="str">
+        <v>その他手当です。ない場合は0を入力します。</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>natura_fasilitas_bkn_uang</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Natura atau fasilitas bukan uang, misalnya fasilitas kendaraan, tempat tinggal, atau fasilitas lain.</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Non-cash benefits or facilities, such as car, housing, or other benefits.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>현금이 아닌 복리후생 또는 시설 제공입니다. 예: 차량, 숙소 등.</v>
+      </c>
+      <c r="E15" t="str">
+        <v>非现金福利或设施，例如车辆、住房等。</v>
+      </c>
+      <c r="F15" t="str">
+        <v>現金以外の福利厚生または施設提供です。例：車両、住宅など。</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>bonus</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Bonus yang dibayarkan pada bulan tersebut.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Bonus paid in the month.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>해당 월에 지급된 보너스입니다.</v>
+      </c>
+      <c r="E16" t="str">
+        <v>当月支付的奖金。</v>
+      </c>
+      <c r="F16" t="str">
+        <v>当月支給された賞与です。</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>THR</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Tunjangan Hari Raya. Isi jika ada pembayaran THR.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Religious holiday allowance. Enter if THR is paid.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>명절수당 THR입니다. 지급한 경우 입력합니다.</v>
+      </c>
+      <c r="E17" t="str">
+        <v>节日津贴 THR。如有支付请填写。</v>
+      </c>
+      <c r="F17" t="str">
+        <v>宗教祝祭手当THRです。支給がある場合に入力します。</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>pinjaman_gaji_loan_from_salary</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Pinjaman atau kasbon karyawan yang akan dipotong dari gaji.</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Employee loan or salary advance deducted from salary.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>급여에서 차감할 직원 대여금 또는 가불금입니다.</v>
+      </c>
+      <c r="E18" t="str">
+        <v>从工资中扣除的员工借款或预支工资。</v>
+      </c>
+      <c r="F18" t="str">
+        <v>給与から控除する従業員貸付金または前払い給与です。</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>potong_gaji_deduction_from_salary</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Potongan gaji lainnya, misalnya denda, koperasi, atau potongan internal.</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Other salary deductions, such as penalties, cooperative fees, or internal deductions.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>기타 급여 공제입니다. 예: 벌금, 조합비, 내부 공제 등.</v>
+      </c>
+      <c r="E19" t="str">
+        <v>其他工资扣除，例如罚款、合作社费用或内部扣除。</v>
+      </c>
+      <c r="F19" t="str">
+        <v>その他給与控除です。例：罰金、組合費、社内控除など。</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>jkk</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Iuran JKK yang ditanggung perusahaan.</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Work accident insurance contribution paid by the company.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>회사 부담 산재보험 JKK입니다.</v>
+      </c>
+      <c r="E20" t="str">
+        <v>公司负担的工伤保险 JKK。</v>
+      </c>
+      <c r="F20" t="str">
+        <v>会社負担の労災保険JKKです。</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>jkm</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Iuran JKM yang ditanggung perusahaan.</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Death insurance contribution paid by the company.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>회사 부담 사망보험 JKM입니다.</v>
+      </c>
+      <c r="E21" t="str">
+        <v>公司负担的死亡保险 JKM。</v>
+      </c>
+      <c r="F21" t="str">
+        <v>会社負担の死亡保障JKMです。</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>jht_company</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Iuran JHT porsi perusahaan.</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Company portion of JHT contribution.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>회사 부담 노후보장 JHT입니다.</v>
+      </c>
+      <c r="E22" t="str">
+        <v>公司负担的 JHT。</v>
+      </c>
+      <c r="F22" t="str">
+        <v>会社負担のJHTです。</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>jp_company</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Iuran JP porsi perusahaan.</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Company portion of pension contribution.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>회사 부담 연금보험 JP입니다.</v>
+      </c>
+      <c r="E23" t="str">
+        <v>公司负担的养老金 JP。</v>
+      </c>
+      <c r="F23" t="str">
+        <v>会社負担の年金JPです。</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>bpjs_kesehatan_company</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Iuran BPJS Kesehatan porsi perusahaan.</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Company portion of BPJS Health contribution.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>회사 부담 BPJS 건강보험입니다.</v>
+      </c>
+      <c r="E24" t="str">
+        <v>公司负担的 BPJS 健康保险。</v>
+      </c>
+      <c r="F24" t="str">
+        <v>会社負担のBPJS健康保険です。</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>JKP_company</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Iuran JKP porsi perusahaan jika ada.</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Company portion of JKP contribution, if any.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>회사 부담 실업보험 JKP입니다. 해당 시 입력합니다.</v>
+      </c>
+      <c r="E25" t="str">
+        <v>公司负担的 JKP，如适用请填写。</v>
+      </c>
+      <c r="F25" t="str">
+        <v>会社負担のJKPです。該当する場合に入力します。</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>jht_employee</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Iuran JHT porsi karyawan yang dipotong dari gaji.</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Employee portion of JHT deducted from salary.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>직원 부담 JHT입니다. 급여에서 공제됩니다.</v>
+      </c>
+      <c r="E26" t="str">
+        <v>员工负担的 JHT，从工资中扣除。</v>
+      </c>
+      <c r="F26" t="str">
+        <v>従業員負担のJHTです。給与から控除されます。</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>jp_employee</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Iuran JP porsi karyawan yang dipotong dari gaji.</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Employee portion of pension contribution deducted from salary.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>직원 부담 JP입니다. 급여에서 공제됩니다.</v>
+      </c>
+      <c r="E27" t="str">
+        <v>员工负担的养老金 JP，从工资中扣除。</v>
+      </c>
+      <c r="F27" t="str">
+        <v>従業員負担の年金JPです。給与から控除されます。</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>bpjs_kesehatan_employee</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Iuran BPJS Kesehatan porsi karyawan yang dipotong dari gaji.</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Employee portion of BPJS Health deducted from salary.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>직원 부담 BPJS 건강보험입니다. 급여에서 공제됩니다.</v>
+      </c>
+      <c r="E28" t="str">
+        <v>员工负担的 BPJS 健康保险，从工资中扣除。</v>
+      </c>
+      <c r="F28" t="str">
+        <v>従業員負担のBPJS健康保険です。給与から控除されます。</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>JKP_employee</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Iuran JKP porsi karyawan jika ada. Jika tidak ada, isi 0.</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Employee portion of JKP contribution, if any. Enter 0 if none.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>직원 부담 JKP입니다. 없으면 0을 입력합니다.</v>
+      </c>
+      <c r="E29" t="str">
+        <v>员工负担的 JKP。如无，填写 0。</v>
+      </c>
+      <c r="F29" t="str">
+        <v>従業員負担のJKPです。ない場合は0を入力します。</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>position</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Jabatan karyawan. Contoh: Manager, Staff, Supervisor.</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Employee position. Example: Manager, Staff, Supervisor.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>직원 직책입니다. 예: Manager, Staff, Supervisor.</v>
+      </c>
+      <c r="E30" t="str">
+        <v>员工职位。例如：经理、员工、主管。</v>
+      </c>
+      <c r="F30" t="str">
+        <v>従業員の役職です。例：Manager、Staff、Supervisor。</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>department</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Departemen tempat karyawan bekerja.</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Department where the employee works.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>직원이 소속된 부서입니다.</v>
+      </c>
+      <c r="E31" t="str">
+        <v>员工所属部门。</v>
+      </c>
+      <c r="F31" t="str">
+        <v>従業員の所属部署です。</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>join_date</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Tanggal mulai bekerja. Gunakan format YYYY-MM-DD.</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Employment start date. Use YYYY-MM-DD format.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>입사일입니다. YYYY-MM-DD 형식으로 입력합니다.</v>
+      </c>
+      <c r="E32" t="str">
+        <v>入职日期。请使用 YYYY-MM-DD 格式。</v>
+      </c>
+      <c r="F32" t="str">
+        <v>入社日です。YYYY-MM-DD形式で入力します。</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>resign_date</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Tanggal berhenti bekerja. Kosongkan jika masih aktif.</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Resignation date. Leave blank if still active.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>퇴사일입니다. 재직 중이면 비워둡니다.</v>
+      </c>
+      <c r="E33" t="str">
+        <v>离职日期。如仍在职，请留空。</v>
+      </c>
+      <c r="F33" t="str">
+        <v>退職日です。在職中の場合は空欄にします。</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>birth_date</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Tanggal lahir karyawan. Gunakan format YYYY-MM-DD.</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Employee date of birth. Use YYYY-MM-DD format.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>직원 생년월일입니다. YYYY-MM-DD 형식으로 입력합니다.</v>
+      </c>
+      <c r="E34" t="str">
+        <v>员工出生日期。请使用 YYYY-MM-DD 格式。</v>
+      </c>
+      <c r="F34" t="str">
+        <v>従業員の生年月日です。YYYY-MM-DD形式で入力します。</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>gender</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Jenis kelamin. Isi M untuk laki-laki, F untuk perempuan.</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Gender. Enter M for male, F for female.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>성별입니다. 남성은 M, 여성은 F를 입력합니다.</v>
+      </c>
+      <c r="E35" t="str">
+        <v>性别。男性填写 M，女性填写 F。</v>
+      </c>
+      <c r="F35" t="str">
+        <v>性別です。男性はM、女性はFを入力します。</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>email</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Alamat email karyawan.</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Employee email address.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>직원 이메일 주소입니다.</v>
+      </c>
+      <c r="E36" t="str">
+        <v>员工电子邮件地址。</v>
+      </c>
+      <c r="F36" t="str">
+        <v>従業員のメールアドレスです。</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>phone</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Nomor telepon atau WhatsApp karyawan.</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Employee phone or WhatsApp number.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>직원 전화번호 또는 WhatsApp 번호입니다.</v>
+      </c>
+      <c r="E37" t="str">
+        <v>员工电话或 WhatsApp 号码。</v>
+      </c>
+      <c r="F37" t="str">
+        <v>従業員の電話番号またはWhatsApp番号です。</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>address</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Alamat tempat tinggal karyawan.</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Employee residential address.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>직원 거주지 주소입니다.</v>
+      </c>
+      <c r="E38" t="str">
+        <v>员工居住地址。</v>
+      </c>
+      <c r="F38" t="str">
+        <v>従業員の住所です。</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>bank_name</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Nama bank untuk pembayaran gaji.</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Bank name for salary payment.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>급여 지급 은행명입니다.</v>
+      </c>
+      <c r="E39" t="str">
+        <v>工资支付银行名称。</v>
+      </c>
+      <c r="F39" t="str">
+        <v>給与支払用の銀行名です。</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>bank_account_no</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Nomor rekening bank karyawan.</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Employee bank account number.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>직원 은행 계좌번호입니다.</v>
+      </c>
+      <c r="E40" t="str">
+        <v>员工银行账号。</v>
+      </c>
+      <c r="F40" t="str">
+        <v>従業員の銀行口座番号です。</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>bank_account_name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Nama pemilik rekening. Biasanya sama dengan nama karyawan.</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Bank account holder name. Usually the same as employee name.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>계좌 예금주 이름입니다. 보통 직원 이름과 동일합니다.</v>
+      </c>
+      <c r="E41" t="str">
+        <v>银行账户持有人姓名，通常与员工姓名一致。</v>
+      </c>
+      <c r="F41" t="str">
+        <v>口座名義人です。通常は従業員名と同じです。</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>emergency_contact_name</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Nama kontak darurat.</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Emergency contact name.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>비상연락처 이름입니다.</v>
+      </c>
+      <c r="E42" t="str">
+        <v>紧急联系人姓名。</v>
+      </c>
+      <c r="F42" t="str">
+        <v>緊急連絡先の氏名です。</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>emergency_contact_phone</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Nomor telepon kontak darurat.</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Emergency contact phone number.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>비상연락처 전화번호입니다.</v>
+      </c>
+      <c r="E43" t="str">
+        <v>紧急联系人电话号码。</v>
+      </c>
+      <c r="F43" t="str">
+        <v>緊急連絡先の電話番号です。</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>notes</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Catatan tambahan jika ada. Contoh: karyawan baru, resign, data belum lengkap.</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Additional notes if any. Example: new employee, resigned, incomplete data.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>추가 메모입니다. 예: 신규 입사, 퇴사, 자료 미완성 등.</v>
+      </c>
+      <c r="E44" t="str">
+        <v>补充说明。例如：新员工、离职、资料不完整等。</v>
+      </c>
+      <c r="F44" t="str">
+        <v>追加メモです。例：新入社員、退職、データ未完了など。</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F44"/>
   </ignoredErrors>
 </worksheet>
 </file>